--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -2256,7 +2256,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr autoPageBreaks="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:FJ118"/>
   <sheetFormatPr defaultColWidth="10.44921875" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.1"/>
@@ -18380,7 +18380,8 @@
     <mergeCell ref="AI3:AS3"/>
     <mergeCell ref="BR3:CQ3"/>
   </mergeCells>
-  <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="53" max="16383" man="1"/>
   </rowBreaks>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -2591,11 +2591,7 @@
       <c r="S6" s="47"/>
       <c r="T6" s="47"/>
       <c r="U6" s="47"/>
-      <c r="V6" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{org_name}}, {{org_address}}, тел. {{org_phone}}</t>
-        </is>
-      </c>
+      <c r="V6" s="47"/>
       <c r="W6" s="47"/>
       <c r="X6" s="47"/>
       <c r="Y6" s="47"/>
@@ -2604,6 +2600,11 @@
       <c r="AB6" s="47"/>
       <c r="AC6" s="47"/>
       <c r="AD6" s="47"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{org_name}}, {{org_address}}, тел. {{org_phone}}</t>
+        </is>
+      </c>
       <c r="EY6" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">{{org_okpo}}</t>
@@ -3408,15 +3409,15 @@
       <c r="BW13" s="51"/>
       <c r="BX13" s="51"/>
       <c r="BY13" s="51"/>
-      <c r="BZ13" s="51" t="inlineStr">
+      <c r="BZ13" s="51"/>
+      <c r="CA13" s="51"/>
+      <c r="CB13" s="51"/>
+      <c r="CC13" s="51"/>
+      <c r="CD13" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">{{vehicle_garage_number}}</t>
         </is>
       </c>
-      <c r="CA13" s="51"/>
-      <c r="CB13" s="51"/>
-      <c r="CC13" s="51"/>
-      <c r="CD13" s="81"/>
       <c r="CE13" s="81"/>
       <c r="CF13" s="81"/>
       <c r="CG13" s="81"/>
@@ -6696,11 +6697,7 @@
       <c r="T42" s="100"/>
       <c r="U42" s="100"/>
       <c r="V42" s="100"/>
-      <c r="W42" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{waybill_number}}</t>
-        </is>
-      </c>
+      <c r="W42" s="100"/>
       <c r="X42" s="100"/>
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
@@ -6715,7 +6712,11 @@
       <c r="AI42" s="100"/>
       <c r="AJ42" s="100"/>
       <c r="AK42" s="100"/>
-      <c r="AL42" s="100"/>
+      <c r="AL42" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{waybill_number}}</t>
+        </is>
+      </c>
       <c r="AM42" s="100"/>
       <c r="AN42" s="100"/>
       <c r="AO42" s="100"/>
@@ -6789,11 +6790,7 @@
       <c r="CY42" s="100"/>
       <c r="CZ42" s="100"/>
       <c r="DA42" s="100"/>
-      <c r="DB42" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{waybill_number}}</t>
-        </is>
-      </c>
+      <c r="DB42" s="100"/>
       <c r="DC42" s="100"/>
       <c r="DD42" s="100"/>
       <c r="DE42" s="100"/>
@@ -6808,7 +6805,11 @@
       <c r="DN42" s="100"/>
       <c r="DO42" s="100"/>
       <c r="DP42" s="100"/>
-      <c r="DQ42" s="100"/>
+      <c r="DQ42" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{waybill_number}}</t>
+        </is>
+      </c>
       <c r="DR42" s="100"/>
       <c r="DS42" s="100"/>
       <c r="DT42" s="100"/>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -11929,7 +11929,11 @@
       <c r="FJ75" s="210"/>
     </row>
     <row r="76" spans="1:166" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A76" s="207"/>
+      <c r="A76" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_from}}</t>
+        </is>
+      </c>
       <c r="B76" s="207"/>
       <c r="C76" s="207"/>
       <c r="D76" s="207"/>
@@ -11953,7 +11957,11 @@
       <c r="V76" s="207"/>
       <c r="W76" s="207"/>
       <c r="X76" s="207"/>
-      <c r="Y76" s="207"/>
+      <c r="Y76" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_to}}</t>
+        </is>
+      </c>
       <c r="Z76" s="207"/>
       <c r="AA76" s="207"/>
       <c r="AB76" s="207"/>
@@ -11974,7 +11982,11 @@
       <c r="AQ76" s="207"/>
       <c r="AR76" s="207"/>
       <c r="AS76" s="207"/>
-      <c r="AT76" s="207"/>
+      <c r="AT76" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_cargo}}</t>
+        </is>
+      </c>
       <c r="AU76" s="207"/>
       <c r="AV76" s="207"/>
       <c r="AW76" s="207"/>
@@ -11987,7 +11999,11 @@
       <c r="BD76" s="207"/>
       <c r="BE76" s="207"/>
       <c r="BF76" s="207"/>
-      <c r="BG76" s="207"/>
+      <c r="BG76" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task2_customer}}</t>
+        </is>
+      </c>
       <c r="BH76" s="207"/>
       <c r="BI76" s="207"/>
       <c r="BJ76" s="207"/>
@@ -12091,7 +12107,11 @@
       <c r="FJ76" s="210"/>
     </row>
     <row r="77" spans="1:166" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A77" s="207"/>
+      <c r="A77" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_from}}</t>
+        </is>
+      </c>
       <c r="B77" s="207"/>
       <c r="C77" s="207"/>
       <c r="D77" s="207"/>
@@ -12115,7 +12135,11 @@
       <c r="V77" s="207"/>
       <c r="W77" s="207"/>
       <c r="X77" s="207"/>
-      <c r="Y77" s="207"/>
+      <c r="Y77" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_to}}</t>
+        </is>
+      </c>
       <c r="Z77" s="207"/>
       <c r="AA77" s="207"/>
       <c r="AB77" s="207"/>
@@ -12136,7 +12160,11 @@
       <c r="AQ77" s="207"/>
       <c r="AR77" s="207"/>
       <c r="AS77" s="207"/>
-      <c r="AT77" s="207"/>
+      <c r="AT77" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_cargo}}</t>
+        </is>
+      </c>
       <c r="AU77" s="207"/>
       <c r="AV77" s="207"/>
       <c r="AW77" s="207"/>
@@ -12149,7 +12177,11 @@
       <c r="BD77" s="207"/>
       <c r="BE77" s="207"/>
       <c r="BF77" s="207"/>
-      <c r="BG77" s="207"/>
+      <c r="BG77" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task3_customer}}</t>
+        </is>
+      </c>
       <c r="BH77" s="207"/>
       <c r="BI77" s="207"/>
       <c r="BJ77" s="207"/>
@@ -12253,7 +12285,11 @@
       <c r="FJ77" s="210"/>
     </row>
     <row r="78" spans="1:166" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A78" s="207"/>
+      <c r="A78" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_from}}</t>
+        </is>
+      </c>
       <c r="B78" s="207"/>
       <c r="C78" s="207"/>
       <c r="D78" s="207"/>
@@ -12277,7 +12313,11 @@
       <c r="V78" s="207"/>
       <c r="W78" s="207"/>
       <c r="X78" s="207"/>
-      <c r="Y78" s="207"/>
+      <c r="Y78" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_to}}</t>
+        </is>
+      </c>
       <c r="Z78" s="207"/>
       <c r="AA78" s="207"/>
       <c r="AB78" s="207"/>
@@ -12298,7 +12338,11 @@
       <c r="AQ78" s="207"/>
       <c r="AR78" s="207"/>
       <c r="AS78" s="207"/>
-      <c r="AT78" s="207"/>
+      <c r="AT78" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_cargo}}</t>
+        </is>
+      </c>
       <c r="AU78" s="207"/>
       <c r="AV78" s="207"/>
       <c r="AW78" s="207"/>
@@ -12311,7 +12355,11 @@
       <c r="BD78" s="207"/>
       <c r="BE78" s="207"/>
       <c r="BF78" s="207"/>
-      <c r="BG78" s="207"/>
+      <c r="BG78" s="207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task4_customer}}</t>
+        </is>
+      </c>
       <c r="BH78" s="207"/>
       <c r="BI78" s="207"/>
       <c r="BJ78" s="207"/>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -5857,9 +5857,7 @@
       <c r="FJ33" s="135"/>
     </row>
     <row r="34" spans="1:166" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A34" s="122" t="s">
-        <v>73</v>
-      </c>
+      <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
       <c r="D34" s="122"/>
@@ -5886,11 +5884,7 @@
       <c r="Y34" s="120"/>
       <c r="Z34" s="120"/>
       <c r="AA34" s="120"/>
-      <c r="AD34" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{dispatcher_fio}}</t>
-        </is>
-      </c>
+      <c r="AD34" s="100"/>
       <c r="AE34" s="100"/>
       <c r="AF34" s="100"/>
       <c r="AG34" s="100"/>
@@ -6005,9 +5999,7 @@
       <c r="K35" s="122"/>
       <c r="L35" s="122"/>
       <c r="M35" s="122"/>
-      <c r="N35" s="43" t="s">
-        <v>77</v>
-      </c>
+      <c r="N35" s="43"/>
       <c r="O35" s="43"/>
       <c r="P35" s="43"/>
       <c r="Q35" s="43"/>
@@ -6021,9 +6013,7 @@
       <c r="Y35" s="43"/>
       <c r="Z35" s="43"/>
       <c r="AA35" s="43"/>
-      <c r="AD35" s="43" t="s">
-        <v>37</v>
-      </c>
+      <c r="AD35" s="43"/>
       <c r="AE35" s="43"/>
       <c r="AF35" s="43"/>
       <c r="AG35" s="43"/>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -1919,54 +1919,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Имя " descr="Descr ">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -18427,6 +18379,5 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="166" max="1048575" man="1"/>
   </colBreaks>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -11766,7 +11766,7 @@
       <c r="BF75" s="207"/>
       <c r="BG75" s="207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{customer_name}}</t>
+          <t xml:space="preserve">{{task_contacts}}</t>
         </is>
       </c>
       <c r="BH75" s="207"/>
@@ -11943,7 +11943,7 @@
       <c r="BF76" s="207"/>
       <c r="BG76" s="207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{task2_customer}}</t>
+          <t xml:space="preserve">{{task2_contacts}}</t>
         </is>
       </c>
       <c r="BH76" s="207"/>
@@ -12121,7 +12121,7 @@
       <c r="BF77" s="207"/>
       <c r="BG77" s="207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{task3_customer}}</t>
+          <t xml:space="preserve">{{task3_contacts}}</t>
         </is>
       </c>
       <c r="BH77" s="207"/>
@@ -12299,7 +12299,7 @@
       <c r="BF78" s="207"/>
       <c r="BG78" s="207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{{task4_customer}}</t>
+          <t xml:space="preserve">{{task4_contacts}}</t>
         </is>
       </c>
       <c r="BH78" s="207"/>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -1225,7 +1225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1901,6 +1901,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true">
+      <alignment wrapText="true" horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true">
+      <alignment wrapText="true" horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true">
+      <alignment wrapText="true" horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11969,7 +11978,11 @@
       <c r="CB76" s="207"/>
       <c r="CC76" s="207"/>
       <c r="CD76" s="207"/>
-      <c r="CG76" s="211"/>
+      <c r="CG76" s="226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task5_line}}</t>
+        </is>
+      </c>
       <c r="CH76" s="211"/>
       <c r="CI76" s="211"/>
       <c r="CJ76" s="211"/>
@@ -12147,7 +12160,11 @@
       <c r="CB77" s="207"/>
       <c r="CC77" s="207"/>
       <c r="CD77" s="207"/>
-      <c r="CG77" s="211"/>
+      <c r="CG77" s="227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task6_line}}</t>
+        </is>
+      </c>
       <c r="CH77" s="211"/>
       <c r="CI77" s="211"/>
       <c r="CJ77" s="211"/>
@@ -12325,7 +12342,11 @@
       <c r="CB78" s="207"/>
       <c r="CC78" s="207"/>
       <c r="CD78" s="207"/>
-      <c r="CG78" s="211"/>
+      <c r="CG78" s="228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{task7_line}}</t>
+        </is>
+      </c>
       <c r="CH78" s="211"/>
       <c r="CI78" s="211"/>
       <c r="CJ78" s="211"/>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -585,7 +585,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1221,11 +1221,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1901,6 +1915,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true">
       <alignment wrapText="true" horizontal="left" vertical="top"/>
@@ -5562,9 +5582,7 @@
       <c r="CO31" s="131"/>
     </row>
     <row r="32" spans="1:166" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A32" s="37" t="s">
-        <v>68</v>
-      </c>
+      <c r="A32" s="37"/>
       <c r="B32" s="37"/>
       <c r="C32" s="37"/>
       <c r="D32" s="37"/>
@@ -5678,9 +5696,7 @@
       <c r="FJ32" s="134"/>
     </row>
     <row r="33" spans="1:166" s="1" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A33" s="37" t="s">
-        <v>70</v>
-      </c>
+      <c r="A33" s="37"/>
       <c r="B33" s="37"/>
       <c r="C33" s="37"/>
       <c r="D33" s="37"/>
@@ -5704,39 +5720,37 @@
       <c r="V33" s="37"/>
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
-      <c r="Y33" s="120"/>
-      <c r="Z33" s="120"/>
-      <c r="AA33" s="120"/>
-      <c r="AB33" s="120"/>
-      <c r="AC33" s="120"/>
-      <c r="AD33" s="120"/>
-      <c r="AE33" s="120"/>
-      <c r="AF33" s="120"/>
-      <c r="AG33" s="120"/>
-      <c r="AH33" s="120"/>
-      <c r="AI33" s="120"/>
-      <c r="AJ33" s="120"/>
-      <c r="AK33" s="120"/>
-      <c r="AL33" s="120"/>
-      <c r="AM33" s="120"/>
-      <c r="AN33" s="120"/>
-      <c r="AO33" s="120"/>
-      <c r="AP33" s="120"/>
-      <c r="AQ33" s="120"/>
-      <c r="AR33" s="120"/>
-      <c r="AS33" s="120"/>
-      <c r="AT33" s="120"/>
-      <c r="AU33" s="120"/>
-      <c r="AV33" s="120"/>
-      <c r="AW33" s="120"/>
-      <c r="AX33" s="120"/>
-      <c r="AY33" s="120"/>
-      <c r="AZ33" s="120"/>
-      <c r="BA33" s="120"/>
-      <c r="BB33" s="120"/>
-      <c r="BC33" s="74" t="s">
-        <v>71</v>
-      </c>
+      <c r="Y33" s="226"/>
+      <c r="Z33" s="226"/>
+      <c r="AA33" s="226"/>
+      <c r="AB33" s="226"/>
+      <c r="AC33" s="226"/>
+      <c r="AD33" s="226"/>
+      <c r="AE33" s="226"/>
+      <c r="AF33" s="226"/>
+      <c r="AG33" s="226"/>
+      <c r="AH33" s="226"/>
+      <c r="AI33" s="226"/>
+      <c r="AJ33" s="226"/>
+      <c r="AK33" s="226"/>
+      <c r="AL33" s="226"/>
+      <c r="AM33" s="226"/>
+      <c r="AN33" s="226"/>
+      <c r="AO33" s="226"/>
+      <c r="AP33" s="226"/>
+      <c r="AQ33" s="226"/>
+      <c r="AR33" s="226"/>
+      <c r="AS33" s="226"/>
+      <c r="AT33" s="226"/>
+      <c r="AU33" s="226"/>
+      <c r="AV33" s="226"/>
+      <c r="AW33" s="226"/>
+      <c r="AX33" s="226"/>
+      <c r="AY33" s="226"/>
+      <c r="AZ33" s="226"/>
+      <c r="BA33" s="226"/>
+      <c r="BB33" s="226"/>
+      <c r="BC33" s="74"/>
       <c r="BD33" s="74"/>
       <c r="BE33" s="74"/>
       <c r="BF33" s="74"/>
@@ -5831,45 +5845,45 @@
       <c r="K34" s="122"/>
       <c r="L34" s="122"/>
       <c r="M34" s="122"/>
-      <c r="N34" s="120"/>
-      <c r="O34" s="120"/>
-      <c r="P34" s="120"/>
-      <c r="Q34" s="120"/>
-      <c r="R34" s="120"/>
-      <c r="S34" s="120"/>
-      <c r="T34" s="120"/>
-      <c r="U34" s="120"/>
-      <c r="V34" s="120"/>
-      <c r="W34" s="120"/>
-      <c r="X34" s="120"/>
-      <c r="Y34" s="120"/>
-      <c r="Z34" s="120"/>
-      <c r="AA34" s="120"/>
-      <c r="AD34" s="100"/>
-      <c r="AE34" s="100"/>
-      <c r="AF34" s="100"/>
-      <c r="AG34" s="100"/>
-      <c r="AH34" s="100"/>
-      <c r="AI34" s="100"/>
-      <c r="AJ34" s="100"/>
-      <c r="AK34" s="100"/>
-      <c r="AL34" s="100"/>
-      <c r="AM34" s="100"/>
-      <c r="AN34" s="100"/>
-      <c r="AO34" s="100"/>
-      <c r="AP34" s="100"/>
-      <c r="AQ34" s="100"/>
-      <c r="AR34" s="100"/>
-      <c r="AS34" s="100"/>
-      <c r="AT34" s="100"/>
-      <c r="AU34" s="100"/>
-      <c r="AV34" s="100"/>
-      <c r="AW34" s="100"/>
-      <c r="AX34" s="100"/>
-      <c r="AY34" s="100"/>
-      <c r="AZ34" s="100"/>
-      <c r="BA34" s="100"/>
-      <c r="BB34" s="100"/>
+      <c r="N34" s="226"/>
+      <c r="O34" s="226"/>
+      <c r="P34" s="226"/>
+      <c r="Q34" s="226"/>
+      <c r="R34" s="226"/>
+      <c r="S34" s="226"/>
+      <c r="T34" s="226"/>
+      <c r="U34" s="226"/>
+      <c r="V34" s="226"/>
+      <c r="W34" s="226"/>
+      <c r="X34" s="226"/>
+      <c r="Y34" s="226"/>
+      <c r="Z34" s="226"/>
+      <c r="AA34" s="226"/>
+      <c r="AD34" s="227"/>
+      <c r="AE34" s="227"/>
+      <c r="AF34" s="227"/>
+      <c r="AG34" s="227"/>
+      <c r="AH34" s="227"/>
+      <c r="AI34" s="227"/>
+      <c r="AJ34" s="227"/>
+      <c r="AK34" s="227"/>
+      <c r="AL34" s="227"/>
+      <c r="AM34" s="227"/>
+      <c r="AN34" s="227"/>
+      <c r="AO34" s="227"/>
+      <c r="AP34" s="227"/>
+      <c r="AQ34" s="227"/>
+      <c r="AR34" s="227"/>
+      <c r="AS34" s="227"/>
+      <c r="AT34" s="227"/>
+      <c r="AU34" s="227"/>
+      <c r="AV34" s="227"/>
+      <c r="AW34" s="227"/>
+      <c r="AX34" s="227"/>
+      <c r="AY34" s="227"/>
+      <c r="AZ34" s="227"/>
+      <c r="BA34" s="227"/>
+      <c r="BB34" s="227"/>
       <c r="CR34" s="122" t="s">
         <v>74</v>
       </c>
@@ -11978,7 +11992,7 @@
       <c r="CB76" s="207"/>
       <c r="CC76" s="207"/>
       <c r="CD76" s="207"/>
-      <c r="CG76" s="226" t="inlineStr">
+      <c r="CG76" s="228" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task5_line}}</t>
         </is>
@@ -12160,7 +12174,7 @@
       <c r="CB77" s="207"/>
       <c r="CC77" s="207"/>
       <c r="CD77" s="207"/>
-      <c r="CG77" s="227" t="inlineStr">
+      <c r="CG77" s="229" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task6_line}}</t>
         </is>
@@ -12342,7 +12356,7 @@
       <c r="CB78" s="207"/>
       <c r="CC78" s="207"/>
       <c r="CD78" s="207"/>
-      <c r="CG78" s="228" t="inlineStr">
+      <c r="CG78" s="230" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task7_line}}</t>
         </is>

--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -585,7 +585,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1235,11 +1235,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1916,11 +1930,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true">
       <alignment wrapText="true" horizontal="left" vertical="top"/>
@@ -3776,9 +3796,7 @@
       <c r="BJ16" s="89"/>
       <c r="BK16" s="89"/>
       <c r="BL16" s="89"/>
-      <c r="CR16" s="90" t="s">
-        <v>34</v>
-      </c>
+      <c r="CR16" s="90"/>
       <c r="CS16" s="90"/>
       <c r="CT16" s="90"/>
       <c r="CU16" s="90"/>
@@ -3810,41 +3828,41 @@
       <c r="DU16" s="90"/>
       <c r="DV16" s="90"/>
       <c r="DW16" s="90"/>
-      <c r="DX16" s="91"/>
-      <c r="DY16" s="91"/>
-      <c r="DZ16" s="91"/>
-      <c r="EA16" s="91"/>
-      <c r="EB16" s="91"/>
-      <c r="EC16" s="91"/>
-      <c r="ED16" s="91"/>
-      <c r="EE16" s="91"/>
-      <c r="EF16" s="91"/>
-      <c r="EG16" s="91"/>
-      <c r="EH16" s="91"/>
-      <c r="EI16" s="91"/>
-      <c r="EJ16" s="91"/>
-      <c r="EM16" s="92"/>
-      <c r="EN16" s="92"/>
-      <c r="EO16" s="92"/>
-      <c r="EP16" s="92"/>
-      <c r="EQ16" s="92"/>
-      <c r="ER16" s="92"/>
-      <c r="ES16" s="92"/>
-      <c r="ET16" s="92"/>
-      <c r="EW16" s="92"/>
-      <c r="EX16" s="92"/>
-      <c r="EY16" s="92"/>
-      <c r="EZ16" s="92"/>
-      <c r="FA16" s="92"/>
-      <c r="FB16" s="92"/>
-      <c r="FC16" s="92"/>
-      <c r="FD16" s="92"/>
-      <c r="FE16" s="92"/>
-      <c r="FF16" s="92"/>
-      <c r="FG16" s="92"/>
-      <c r="FH16" s="92"/>
-      <c r="FI16" s="92"/>
-      <c r="FJ16" s="92"/>
+      <c r="DX16" s="226"/>
+      <c r="DY16" s="226"/>
+      <c r="DZ16" s="226"/>
+      <c r="EA16" s="226"/>
+      <c r="EB16" s="226"/>
+      <c r="EC16" s="226"/>
+      <c r="ED16" s="226"/>
+      <c r="EE16" s="226"/>
+      <c r="EF16" s="226"/>
+      <c r="EG16" s="226"/>
+      <c r="EH16" s="226"/>
+      <c r="EI16" s="226"/>
+      <c r="EJ16" s="226"/>
+      <c r="EM16" s="229"/>
+      <c r="EN16" s="229"/>
+      <c r="EO16" s="229"/>
+      <c r="EP16" s="229"/>
+      <c r="EQ16" s="229"/>
+      <c r="ER16" s="229"/>
+      <c r="ES16" s="229"/>
+      <c r="ET16" s="229"/>
+      <c r="EW16" s="229"/>
+      <c r="EX16" s="229"/>
+      <c r="EY16" s="229"/>
+      <c r="EZ16" s="229"/>
+      <c r="FA16" s="229"/>
+      <c r="FB16" s="229"/>
+      <c r="FC16" s="229"/>
+      <c r="FD16" s="229"/>
+      <c r="FE16" s="229"/>
+      <c r="FF16" s="229"/>
+      <c r="FG16" s="229"/>
+      <c r="FH16" s="229"/>
+      <c r="FI16" s="229"/>
+      <c r="FJ16" s="229"/>
     </row>
     <row r="17" spans="1:166" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.1">
       <c r="A17" s="74" t="s">
@@ -3897,9 +3915,7 @@
       <c r="AP17" s="88"/>
       <c r="AQ17" s="88"/>
       <c r="AR17" s="88"/>
-      <c r="EM17" s="93" t="s">
-        <v>36</v>
-      </c>
+      <c r="EM17" s="93"/>
       <c r="EN17" s="93"/>
       <c r="EO17" s="93"/>
       <c r="EP17" s="93"/>
@@ -3907,9 +3923,7 @@
       <c r="ER17" s="93"/>
       <c r="ES17" s="93"/>
       <c r="ET17" s="93"/>
-      <c r="EW17" s="93" t="s">
-        <v>37</v>
-      </c>
+      <c r="EW17" s="93"/>
       <c r="EX17" s="93"/>
       <c r="EY17" s="93"/>
       <c r="EZ17" s="93"/>
@@ -5656,7 +5670,11 @@
       <c r="DU32" s="133"/>
       <c r="DV32" s="133"/>
       <c r="DW32" s="133"/>
-      <c r="DY32" s="134"/>
+      <c r="DY32" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{driver_short_name}}</t>
+        </is>
+      </c>
       <c r="DZ32" s="134"/>
       <c r="EA32" s="134"/>
       <c r="EB32" s="134"/>
@@ -5720,36 +5738,36 @@
       <c r="V33" s="37"/>
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
-      <c r="Y33" s="226"/>
-      <c r="Z33" s="226"/>
-      <c r="AA33" s="226"/>
-      <c r="AB33" s="226"/>
-      <c r="AC33" s="226"/>
-      <c r="AD33" s="226"/>
-      <c r="AE33" s="226"/>
-      <c r="AF33" s="226"/>
-      <c r="AG33" s="226"/>
-      <c r="AH33" s="226"/>
-      <c r="AI33" s="226"/>
-      <c r="AJ33" s="226"/>
-      <c r="AK33" s="226"/>
-      <c r="AL33" s="226"/>
-      <c r="AM33" s="226"/>
-      <c r="AN33" s="226"/>
-      <c r="AO33" s="226"/>
-      <c r="AP33" s="226"/>
-      <c r="AQ33" s="226"/>
-      <c r="AR33" s="226"/>
-      <c r="AS33" s="226"/>
-      <c r="AT33" s="226"/>
-      <c r="AU33" s="226"/>
-      <c r="AV33" s="226"/>
-      <c r="AW33" s="226"/>
-      <c r="AX33" s="226"/>
-      <c r="AY33" s="226"/>
-      <c r="AZ33" s="226"/>
-      <c r="BA33" s="226"/>
-      <c r="BB33" s="226"/>
+      <c r="Y33" s="227"/>
+      <c r="Z33" s="227"/>
+      <c r="AA33" s="227"/>
+      <c r="AB33" s="227"/>
+      <c r="AC33" s="227"/>
+      <c r="AD33" s="227"/>
+      <c r="AE33" s="227"/>
+      <c r="AF33" s="227"/>
+      <c r="AG33" s="227"/>
+      <c r="AH33" s="227"/>
+      <c r="AI33" s="227"/>
+      <c r="AJ33" s="227"/>
+      <c r="AK33" s="227"/>
+      <c r="AL33" s="227"/>
+      <c r="AM33" s="227"/>
+      <c r="AN33" s="227"/>
+      <c r="AO33" s="227"/>
+      <c r="AP33" s="227"/>
+      <c r="AQ33" s="227"/>
+      <c r="AR33" s="227"/>
+      <c r="AS33" s="227"/>
+      <c r="AT33" s="227"/>
+      <c r="AU33" s="227"/>
+      <c r="AV33" s="227"/>
+      <c r="AW33" s="227"/>
+      <c r="AX33" s="227"/>
+      <c r="AY33" s="227"/>
+      <c r="AZ33" s="227"/>
+      <c r="BA33" s="227"/>
+      <c r="BB33" s="227"/>
       <c r="BC33" s="74"/>
       <c r="BD33" s="74"/>
       <c r="BE33" s="74"/>
@@ -5845,45 +5863,45 @@
       <c r="K34" s="122"/>
       <c r="L34" s="122"/>
       <c r="M34" s="122"/>
-      <c r="N34" s="226"/>
-      <c r="O34" s="226"/>
-      <c r="P34" s="226"/>
-      <c r="Q34" s="226"/>
-      <c r="R34" s="226"/>
-      <c r="S34" s="226"/>
-      <c r="T34" s="226"/>
-      <c r="U34" s="226"/>
-      <c r="V34" s="226"/>
-      <c r="W34" s="226"/>
-      <c r="X34" s="226"/>
-      <c r="Y34" s="226"/>
-      <c r="Z34" s="226"/>
-      <c r="AA34" s="226"/>
-      <c r="AD34" s="227"/>
-      <c r="AE34" s="227"/>
-      <c r="AF34" s="227"/>
-      <c r="AG34" s="227"/>
-      <c r="AH34" s="227"/>
-      <c r="AI34" s="227"/>
-      <c r="AJ34" s="227"/>
-      <c r="AK34" s="227"/>
-      <c r="AL34" s="227"/>
-      <c r="AM34" s="227"/>
-      <c r="AN34" s="227"/>
-      <c r="AO34" s="227"/>
-      <c r="AP34" s="227"/>
-      <c r="AQ34" s="227"/>
-      <c r="AR34" s="227"/>
-      <c r="AS34" s="227"/>
-      <c r="AT34" s="227"/>
-      <c r="AU34" s="227"/>
-      <c r="AV34" s="227"/>
-      <c r="AW34" s="227"/>
-      <c r="AX34" s="227"/>
-      <c r="AY34" s="227"/>
-      <c r="AZ34" s="227"/>
-      <c r="BA34" s="227"/>
-      <c r="BB34" s="227"/>
+      <c r="N34" s="227"/>
+      <c r="O34" s="227"/>
+      <c r="P34" s="227"/>
+      <c r="Q34" s="227"/>
+      <c r="R34" s="227"/>
+      <c r="S34" s="227"/>
+      <c r="T34" s="227"/>
+      <c r="U34" s="227"/>
+      <c r="V34" s="227"/>
+      <c r="W34" s="227"/>
+      <c r="X34" s="227"/>
+      <c r="Y34" s="227"/>
+      <c r="Z34" s="227"/>
+      <c r="AA34" s="227"/>
+      <c r="AD34" s="228"/>
+      <c r="AE34" s="228"/>
+      <c r="AF34" s="228"/>
+      <c r="AG34" s="228"/>
+      <c r="AH34" s="228"/>
+      <c r="AI34" s="228"/>
+      <c r="AJ34" s="228"/>
+      <c r="AK34" s="228"/>
+      <c r="AL34" s="228"/>
+      <c r="AM34" s="228"/>
+      <c r="AN34" s="228"/>
+      <c r="AO34" s="228"/>
+      <c r="AP34" s="228"/>
+      <c r="AQ34" s="228"/>
+      <c r="AR34" s="228"/>
+      <c r="AS34" s="228"/>
+      <c r="AT34" s="228"/>
+      <c r="AU34" s="228"/>
+      <c r="AV34" s="228"/>
+      <c r="AW34" s="228"/>
+      <c r="AX34" s="228"/>
+      <c r="AY34" s="228"/>
+      <c r="AZ34" s="228"/>
+      <c r="BA34" s="228"/>
+      <c r="BB34" s="228"/>
       <c r="CR34" s="122" t="s">
         <v>74</v>
       </c>
@@ -6190,7 +6208,11 @@
       <c r="DJ37" s="139"/>
       <c r="DK37" s="139"/>
       <c r="DL37" s="139"/>
-      <c r="DN37" s="57"/>
+      <c r="DN37" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{driver_short_name}}</t>
+        </is>
+      </c>
       <c r="DO37" s="57"/>
       <c r="DP37" s="57"/>
       <c r="DQ37" s="57"/>
@@ -11992,7 +12014,7 @@
       <c r="CB76" s="207"/>
       <c r="CC76" s="207"/>
       <c r="CD76" s="207"/>
-      <c r="CG76" s="228" t="inlineStr">
+      <c r="CG76" s="230" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task5_line}}</t>
         </is>
@@ -12174,7 +12196,7 @@
       <c r="CB77" s="207"/>
       <c r="CC77" s="207"/>
       <c r="CD77" s="207"/>
-      <c r="CG77" s="229" t="inlineStr">
+      <c r="CG77" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task6_line}}</t>
         </is>
@@ -12356,7 +12378,7 @@
       <c r="CB78" s="207"/>
       <c r="CC78" s="207"/>
       <c r="CD78" s="207"/>
-      <c r="CG78" s="230" t="inlineStr">
+      <c r="CG78" s="232" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task7_line}}</t>
         </is>
